--- a/template/映射规则.xlsx
+++ b/template/映射规则.xlsx
@@ -1477,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1630,6 +1630,78 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>📋 操作记录说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>合并完成后，输出目录下会生成「操作记录.xlsx」，包含两个 sheet：</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>【合并映射明细】  每条数据的完整来龙去脉：</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    源文件名 → 源文件行号 → 收款户名/收款账号/金额 → 归类大单位 → 输出文件名 → 输出文件行号</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    金额为0的数据也在操作记录中保留，方便核对。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>【汇总】  统计总文件数、总行数、排除项行数、各输出文件的明细。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>⚠ 金额过滤说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    生成报盘文件时，金额为0的行自动剔除（不写入输出 xlsx），</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    但操作记录中完整保留，确保数据可追溯。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/template/映射规则.xlsx
+++ b/template/映射规则.xlsx
@@ -1664,7 +1664,7 @@
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    金额为0的数据也在操作记录中保留，方便核对。</t>
+          <t xml:space="preserve">    金额为0的数据也在操作记录中保留，备注列标注「金额为0，已过滤」（粉红底色），方便核对。</t>
         </is>
       </c>
     </row>

--- a/template/映射规则.xlsx
+++ b/template/映射规则.xlsx
@@ -640,7 +640,11 @@
           <t>中建银（北京）房地产土地资产评估有限公司</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr"/>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>中建银（北京）房地产土地资产评估有限公司</t>
+        </is>
+      </c>
       <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Y</t>

--- a/template/映射规则.xlsx
+++ b/template/映射规则.xlsx
@@ -598,7 +598,11 @@
           <t>吉林省交通实业发展有限公司</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr"/>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>吉林省交通实业发展有限公司</t>
+        </is>
+      </c>
       <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -619,7 +623,11 @@
           <t>吉林省高等学校毕业生就业指导中心</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr"/>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>吉林省高等学校毕业生就业指导中心</t>
+        </is>
+      </c>
       <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -665,7 +673,11 @@
           <t>供销粮油吉林有限公司</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>供销粮油吉林有限公司</t>
+        </is>
+      </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -686,7 +698,11 @@
           <t>平高集团华生电力设计有限公司</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>平高集团华生电力设计有限公司</t>
+        </is>
+      </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -707,7 +723,11 @@
           <t>中国邮政储蓄银行股份有限公司吉林省分行直属支行</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>中国邮政储蓄银行股份有限公司吉林省分行直属支行</t>
+        </is>
+      </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -728,7 +748,11 @@
           <t>国家税务总局长春净月高新技术产业开发区税务局</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>国家税务总局长春净月高新技术产业开发区税务局</t>
+        </is>
+      </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
           <t>Y</t>
@@ -959,7 +983,11 @@
           <t>吉林银行</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>吉林银行</t>
+        </is>
+      </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Y</t>

--- a/template/映射规则.xlsx
+++ b/template/映射规则.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -183,6 +183,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1509,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1734,6 +1737,179 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>📋 重复报盘检测说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>合并完成后，程序会扫描所有已读取的记录，按以下规则判断是否为重复报盘：</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>【判重规则】</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  同时满足以下 5 个条件时，判定为可能重复报盘：</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ① 同一大单位（归类后的大单位名相同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ② 同一年月（源月份相同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ③ 收款户名相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ④ 收款账号相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ⑤ 金额相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="29" t="inlineStr">
+        <is>
+          <t>【触发示例】</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  例1: 单位「XXX公司」与「XXX公司 - 副本」为同一大单位，</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        同月给同一人发了同一金额 → 触发重复警告</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  例2: 某人的 (1)(2)(3)(4) 四个变体文件，</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        同月给同一人发了同一金额 → 触发重复警告</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="29" t="inlineStr">
+        <is>
+          <t>【注意】</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 不同月份同一人同一金额 → 正常情况，不判重</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 金额为 0 的行不参与判重</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 户名和账号都为空的行不参与判重</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="28" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>【检测结果】</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • GUI 日志区列出每条重复详情</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 弹出警告框汇总条数</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 操作记录.xlsx 中重复行标注「可能重复报盘」（黄色底色）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • 重复不会阻止文件生成，仅作提示，由人工确认</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/template/映射规则.xlsx
+++ b/template/映射规则.xlsx
@@ -1512,7 +1512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:A88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1910,6 +1910,133 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
+        <is>
+          <t>📋 单位名规范化说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>读取文件时，源单位名会自动去除 Windows 复制文件产生的后缀，作为回退的大单位名：</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  去除的后缀模式：</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    （1）（2）...   → 公司名（1）→ 公司名</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 副本          → 公司名 - 副本 → 公司名</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - Copy / - copy → 公司名 - Copy → 公司名</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 复件          → 公司名 - 复件 → 公司名</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    _副本           → 公司名_副本   → 公司名</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  效果：即使文件名带 (1)(2) 或「- 副本」等后缀，</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        未在映射规则表中的单位也能按规范化名跨文件判重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>📋 文件级重复检测说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
+        <is>
+          <t>全局判重完成后，程序会额外检查是否有源文件的全部记录都被判为重复：</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  触发条件：源文件中所有非过滤记录均被标记为「可能重复报盘」</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  判断逻辑：比较源文件之间的去重 key 集合，完全相同则判定为文件复制</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  示例：A公司-202504.xls 与 A公司-202504(1).xls 内容完全一致 → 触发警告</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  注意：文件级重复不会阻止文件生成，仅作提示，由人工确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
